--- a/ig/main/CodeSystem-service-type.xlsx
+++ b/ig/main/CodeSystem-service-type.xlsx
@@ -84,7 +84,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>
